--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487158_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487158_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.8416</v>
+        <v>5.1053</v>
       </c>
       <c r="E2" t="n">
-        <v>3.5597</v>
+        <v>4.1982</v>
       </c>
       <c r="F2" t="n">
-        <v>1.2819</v>
+        <v>0.9071</v>
       </c>
       <c r="G2" t="n">
         <v>3.8395</v>
@@ -610,13 +610,13 @@
         <v>2.1231</v>
       </c>
       <c r="S2" t="n">
-        <v>-1.0788</v>
+        <v>-0.8149999999999999</v>
       </c>
       <c r="T2" t="n">
-        <v>-1.8441</v>
+        <v>-1.2056</v>
       </c>
       <c r="U2" t="n">
-        <v>0.7654</v>
+        <v>0.3906</v>
       </c>
       <c r="V2" t="n">
         <v>-0.0422</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.3575</v>
+        <v>3.7699</v>
       </c>
       <c r="E3" t="n">
-        <v>1.562</v>
+        <v>2.0815</v>
       </c>
       <c r="F3" t="n">
-        <v>1.7954</v>
+        <v>1.6884</v>
       </c>
       <c r="G3" t="n">
         <v>6.4739</v>
@@ -688,13 +688,13 @@
         <v>2.3161</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.7231</v>
+        <v>-0.3107</v>
       </c>
       <c r="T3" t="n">
-        <v>-1.2492</v>
+        <v>-0.7297</v>
       </c>
       <c r="U3" t="n">
-        <v>0.5261</v>
+        <v>0.419</v>
       </c>
       <c r="V3" t="n">
         <v>-0.6562</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.3885</v>
+        <v>1.1664</v>
       </c>
       <c r="E4" t="n">
-        <v>-1.4937</v>
+        <v>-1.4748</v>
       </c>
       <c r="F4" t="n">
-        <v>2.8821</v>
+        <v>2.6412</v>
       </c>
       <c r="G4" t="n">
         <v>-0.4725</v>
@@ -766,13 +766,13 @@
         <v>2.1231</v>
       </c>
       <c r="S4" t="n">
-        <v>0.5678</v>
+        <v>0.3457</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.4032</v>
+        <v>-0.3843</v>
       </c>
       <c r="U4" t="n">
-        <v>0.971</v>
+        <v>0.73</v>
       </c>
       <c r="V4" t="n">
         <v>0.3281</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>J. GOMEZ MERODIO</t>
+          <t>L. MAESTRO STEELE</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.3378</v>
+        <v>0.1988</v>
       </c>
       <c r="E5" t="n">
-        <v>0.7936</v>
+        <v>0.0162</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.1314</v>
+        <v>0.1826</v>
       </c>
       <c r="G5" t="n">
-        <v>0.6223</v>
+        <v>1.9327</v>
       </c>
       <c r="H5" t="n">
-        <v>0.9315</v>
+        <v>-0.6085</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.3092</v>
+        <v>2.5412</v>
       </c>
       <c r="J5" t="n">
-        <v>1.329</v>
+        <v>2.6197</v>
       </c>
       <c r="K5" t="n">
-        <v>0.6778</v>
+        <v>-0.4813</v>
       </c>
       <c r="L5" t="n">
-        <v>0.6512</v>
+        <v>3.101</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.7067</v>
+        <v>-0.6870000000000001</v>
       </c>
       <c r="N5" t="n">
-        <v>0.2536</v>
+        <v>-0.1272</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.9604</v>
+        <v>-0.5598</v>
       </c>
       <c r="P5" t="n">
-        <v>0.193</v>
+        <v>0.386</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-1.158</v>
       </c>
       <c r="R5" t="n">
-        <v>0.193</v>
+        <v>1.5441</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.8672</v>
+        <v>-0.5638</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.5354</v>
+        <v>-0.7892</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.3318</v>
+        <v>0.2254</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.2859</v>
+        <v>-1.5561</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>-0.6562</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.2859</v>
+        <v>-0.8999</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>L. MAESTRO STEELE</t>
+          <t>J. GOMEZ MERODIO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.3742</v>
+        <v>-0.0047</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.5033</v>
+        <v>0.9126</v>
       </c>
       <c r="F6" t="n">
-        <v>0.1291</v>
+        <v>-0.9173</v>
       </c>
       <c r="G6" t="n">
-        <v>1.9327</v>
+        <v>0.6223</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.6085</v>
+        <v>0.9315</v>
       </c>
       <c r="I6" t="n">
-        <v>2.5412</v>
+        <v>-0.3092</v>
       </c>
       <c r="J6" t="n">
-        <v>2.6197</v>
+        <v>1.329</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.4813</v>
+        <v>0.6778</v>
       </c>
       <c r="L6" t="n">
-        <v>3.101</v>
+        <v>0.6512</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.6870000000000001</v>
+        <v>-0.7067</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.1272</v>
+        <v>0.2536</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.5598</v>
+        <v>-0.9604</v>
       </c>
       <c r="P6" t="n">
-        <v>0.386</v>
+        <v>0.193</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.158</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.5441</v>
+        <v>0.193</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.1369</v>
+        <v>-0.5341</v>
       </c>
       <c r="T6" t="n">
-        <v>-1.3087</v>
+        <v>-0.4164</v>
       </c>
       <c r="U6" t="n">
-        <v>0.1718</v>
+        <v>-0.1177</v>
       </c>
       <c r="V6" t="n">
-        <v>-1.5561</v>
+        <v>-0.2859</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.6562</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.8999</v>
+        <v>-0.2859</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-2.3788</v>
+        <v>-2.1528</v>
       </c>
       <c r="E7" t="n">
-        <v>-2.7897</v>
+        <v>-2.6707</v>
       </c>
       <c r="F7" t="n">
-        <v>0.4109</v>
+        <v>0.518</v>
       </c>
       <c r="G7" t="n">
         <v>-1.5435</v>
@@ -1000,13 +1000,13 @@
         <v>0.579</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.8196</v>
+        <v>-0.5936</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.6544</v>
+        <v>-0.5354</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.1653</v>
+        <v>-0.0582</v>
       </c>
       <c r="V7" t="n">
         <v>0.3704</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>M. CARCOBA BEDIA</t>
+          <t>H. SAIZ-BUSTAMANTE GOMEZ</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-3.3817</v>
+        <v>-2.935</v>
       </c>
       <c r="E8" t="n">
-        <v>-3.5084</v>
+        <v>-0.3689</v>
       </c>
       <c r="F8" t="n">
-        <v>0.1267</v>
+        <v>-2.5661</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.6047</v>
+        <v>-0.6563</v>
       </c>
       <c r="H8" t="n">
-        <v>3.2996</v>
+        <v>0.6904</v>
       </c>
       <c r="I8" t="n">
-        <v>-3.9042</v>
+        <v>-1.3466</v>
       </c>
       <c r="J8" t="n">
-        <v>0.9756</v>
+        <v>1.7321</v>
       </c>
       <c r="K8" t="n">
-        <v>2.0181</v>
+        <v>0.3569</v>
       </c>
       <c r="L8" t="n">
-        <v>-1.0424</v>
+        <v>1.3752</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.5803</v>
+        <v>-2.3884</v>
       </c>
       <c r="N8" t="n">
-        <v>1.2815</v>
+        <v>0.3335</v>
       </c>
       <c r="O8" t="n">
-        <v>-2.8618</v>
+        <v>-2.7219</v>
       </c>
       <c r="P8" t="n">
-        <v>-2.3161</v>
+        <v>-0.579</v>
       </c>
       <c r="Q8" t="n">
-        <v>-3.8602</v>
+        <v>-2.1231</v>
       </c>
       <c r="R8" t="n">
         <v>1.5441</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.1329</v>
+        <v>-0.8421</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.5816</v>
+        <v>-0.5919</v>
       </c>
       <c r="U8" t="n">
-        <v>0.4488</v>
+        <v>-0.2502</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.3281</v>
+        <v>-0.8576</v>
       </c>
       <c r="W8" t="n">
-        <v>-0.0422</v>
+        <v>0.614</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.2859</v>
+        <v>-1.4716</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>H. SAIZ-BUSTAMANTE GOMEZ</t>
+          <t>M. CARCOBA BEDIA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-3.5953</v>
+        <v>-3.697</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.7883</v>
+        <v>-3.6899</v>
       </c>
       <c r="F9" t="n">
-        <v>-2.8071</v>
+        <v>-0.0072</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.6563</v>
+        <v>-0.6047</v>
       </c>
       <c r="H9" t="n">
-        <v>0.6904</v>
+        <v>3.2996</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.3466</v>
+        <v>-3.9042</v>
       </c>
       <c r="J9" t="n">
-        <v>1.7321</v>
+        <v>0.9756</v>
       </c>
       <c r="K9" t="n">
-        <v>0.3569</v>
+        <v>2.0181</v>
       </c>
       <c r="L9" t="n">
-        <v>1.3752</v>
+        <v>-1.0424</v>
       </c>
       <c r="M9" t="n">
-        <v>-2.3884</v>
+        <v>-1.5803</v>
       </c>
       <c r="N9" t="n">
-        <v>0.3335</v>
+        <v>1.2815</v>
       </c>
       <c r="O9" t="n">
-        <v>-2.7219</v>
+        <v>-2.8618</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.579</v>
+        <v>-2.3161</v>
       </c>
       <c r="Q9" t="n">
-        <v>-2.1231</v>
+        <v>-3.8602</v>
       </c>
       <c r="R9" t="n">
         <v>1.5441</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.5024</v>
+        <v>-0.4482</v>
       </c>
       <c r="T9" t="n">
-        <v>-1.0113</v>
+        <v>-0.7631</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.4911</v>
+        <v>0.3149</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.8576</v>
+        <v>-0.3281</v>
       </c>
       <c r="W9" t="n">
-        <v>0.614</v>
+        <v>-0.0422</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.4716</v>
+        <v>-0.2859</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-6.1093</v>
+        <v>-6.851</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.6689</v>
+        <v>-3.6515</v>
       </c>
       <c r="F10" t="n">
-        <v>-3.4404</v>
+        <v>-3.1995</v>
       </c>
       <c r="G10" t="n">
         <v>-3.1486</v>
@@ -1234,13 +1234,13 @@
         <v>1.5441</v>
       </c>
       <c r="S10" t="n">
-        <v>0.0549</v>
+        <v>-0.6868</v>
       </c>
       <c r="T10" t="n">
-        <v>0.8131</v>
+        <v>-0.1695</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.7582</v>
+        <v>-0.5173</v>
       </c>
       <c r="V10" t="n">
         <v>-1.4716</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-6.5895</v>
+        <v>-5.400100000000001</v>
       </c>
       <c r="E11" t="n">
-        <v>-5.836999999999999</v>
+        <v>-4.647300000000001</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.7527999999999997</v>
+        <v>-0.7528000000000001</v>
       </c>
       <c r="G11" t="n">
         <v>6.442800000000002</v>
@@ -1282,7 +1282,7 @@
         <v>9.113399999999999</v>
       </c>
       <c r="I11" t="n">
-        <v>-2.670500000000001</v>
+        <v>-2.6705</v>
       </c>
       <c r="J11" t="n">
         <v>16.6128</v>
@@ -1312,13 +1312,13 @@
         <v>13.5107</v>
       </c>
       <c r="S11" t="n">
-        <v>-5.638199999999999</v>
+        <v>-4.4486</v>
       </c>
       <c r="T11" t="n">
-        <v>-6.7748</v>
+        <v>-5.5851</v>
       </c>
       <c r="U11" t="n">
-        <v>1.1367</v>
+        <v>1.1365</v>
       </c>
       <c r="V11" t="n">
         <v>-4.4992</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>8.0831</v>
+        <v>8.470800000000001</v>
       </c>
       <c r="E12" t="n">
-        <v>6.4755</v>
+        <v>6.6758</v>
       </c>
       <c r="F12" t="n">
-        <v>1.6076</v>
+        <v>1.795</v>
       </c>
       <c r="G12" t="n">
         <v>7.591</v>
@@ -1390,13 +1390,13 @@
         <v>2.3161</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.1871</v>
+        <v>0.2006</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.9373</v>
+        <v>-0.737</v>
       </c>
       <c r="U12" t="n">
-        <v>0.7502</v>
+        <v>0.9376</v>
       </c>
       <c r="V12" t="n">
         <v>-0.2859</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>4.8116</v>
+        <v>5.6474</v>
       </c>
       <c r="E13" t="n">
-        <v>2.7205</v>
+        <v>3.021</v>
       </c>
       <c r="F13" t="n">
-        <v>2.0911</v>
+        <v>2.6264</v>
       </c>
       <c r="G13" t="n">
         <v>0.7419</v>
@@ -1468,13 +1468,13 @@
         <v>2.7021</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.5949</v>
+        <v>0.2409</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.8037</v>
+        <v>-0.5033</v>
       </c>
       <c r="U13" t="n">
-        <v>0.2089</v>
+        <v>0.7442</v>
       </c>
       <c r="V13" t="n">
         <v>3.3135</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>1.1303</v>
+        <v>1.3911</v>
       </c>
       <c r="E14" t="n">
-        <v>2.141</v>
+        <v>2.2411</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.0107</v>
+        <v>-0.85</v>
       </c>
       <c r="G14" t="n">
         <v>0.3265</v>
@@ -1546,13 +1546,13 @@
         <v>0.772</v>
       </c>
       <c r="S14" t="n">
-        <v>0.0317</v>
+        <v>0.2925</v>
       </c>
       <c r="T14" t="n">
-        <v>0.0727</v>
+        <v>0.1729</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.041</v>
+        <v>0.1196</v>
       </c>
       <c r="V14" t="n">
         <v>0</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.6912</v>
+        <v>0.2639</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.4391</v>
+        <v>-0.8397</v>
       </c>
       <c r="F15" t="n">
-        <v>1.1303</v>
+        <v>1.1035</v>
       </c>
       <c r="G15" t="n">
         <v>-0.885</v>
@@ -1624,13 +1624,13 @@
         <v>2.1231</v>
       </c>
       <c r="S15" t="n">
-        <v>1.8224</v>
+        <v>1.395</v>
       </c>
       <c r="T15" t="n">
-        <v>0.6491</v>
+        <v>0.2486</v>
       </c>
       <c r="U15" t="n">
-        <v>1.1732</v>
+        <v>1.1464</v>
       </c>
       <c r="V15" t="n">
         <v>2.4559</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>I. SAGASTI ARGOTE</t>
+          <t>J. EGAA AYERZA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.604</v>
+        <v>-0.2485</v>
       </c>
       <c r="E16" t="n">
-        <v>1.5005</v>
+        <v>-0.1244</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.8965</v>
+        <v>-0.1241</v>
       </c>
       <c r="G16" t="n">
-        <v>-2.0503</v>
+        <v>-1.4727</v>
       </c>
       <c r="H16" t="n">
-        <v>-2.0731</v>
+        <v>-0.5723</v>
       </c>
       <c r="I16" t="n">
-        <v>0.0228</v>
+        <v>-0.9004</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.5155</v>
+        <v>-0.0114</v>
       </c>
       <c r="K16" t="n">
-        <v>-1.8993</v>
+        <v>0.0621</v>
       </c>
       <c r="L16" t="n">
-        <v>1.3838</v>
+        <v>-0.0735</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.5347</v>
+        <v>-1.4612</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.1738</v>
+        <v>-0.6344</v>
       </c>
       <c r="O16" t="n">
-        <v>-1.3609</v>
+        <v>-0.8268</v>
       </c>
       <c r="P16" t="n">
-        <v>0.965</v>
+        <v>0.772</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>-0.193</v>
       </c>
       <c r="R16" t="n">
         <v>0.965</v>
       </c>
       <c r="S16" t="n">
-        <v>1.9751</v>
+        <v>0.1662</v>
       </c>
       <c r="T16" t="n">
-        <v>2.016</v>
+        <v>-0.2059</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.041</v>
+        <v>0.3721</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.2859</v>
+        <v>0.2859</v>
       </c>
       <c r="W16" t="n">
+        <v>0.2859</v>
+      </c>
+      <c r="X16" t="n">
         <v>0</v>
-      </c>
-      <c r="X16" t="n">
-        <v>-0.2859</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X. OSTOLAZA OSTOLAZA</t>
+          <t>I. SAGASTI ARGOTE</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.5959</v>
+        <v>-0.3369</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.0579</v>
+        <v>0.399</v>
       </c>
       <c r="F17" t="n">
-        <v>0.462</v>
+        <v>-0.7359</v>
       </c>
       <c r="G17" t="n">
-        <v>-1.1808</v>
+        <v>-2.0503</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.9481000000000001</v>
+        <v>-2.0731</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.2328</v>
+        <v>0.0228</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.6269</v>
+        <v>-0.5155</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.6676</v>
+        <v>-1.8993</v>
       </c>
       <c r="L17" t="n">
-        <v>0.0407</v>
+        <v>1.3838</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.5538999999999999</v>
+        <v>-1.5347</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.2805</v>
+        <v>-0.1738</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.2735</v>
+        <v>-1.3609</v>
       </c>
       <c r="P17" t="n">
-        <v>0.579</v>
+        <v>0.965</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0.193</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>0.772</v>
+        <v>0.965</v>
       </c>
       <c r="S17" t="n">
-        <v>0.0059</v>
+        <v>1.0341</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.238</v>
+        <v>0.9145</v>
       </c>
       <c r="U17" t="n">
-        <v>0.2439</v>
+        <v>0.1196</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>-0.2859</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>-0.2859</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>J. EGAA AYERZA</t>
+          <t>X. OSTOLAZA OSTOLAZA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,64 +1813,64 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.6025</v>
+        <v>-0.576</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.4249</v>
+        <v>-0.9577</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.1776</v>
+        <v>0.3817</v>
       </c>
       <c r="G18" t="n">
-        <v>-1.4727</v>
+        <v>-1.1808</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.5723</v>
+        <v>-0.9481000000000001</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.9004</v>
+        <v>-0.2328</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.0114</v>
+        <v>-0.6269</v>
       </c>
       <c r="K18" t="n">
-        <v>0.0621</v>
+        <v>-0.6676</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.0735</v>
+        <v>0.0407</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.4612</v>
+        <v>-0.5538999999999999</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.6344</v>
+        <v>-0.2805</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.8268</v>
+        <v>-0.2735</v>
       </c>
       <c r="P18" t="n">
-        <v>0.772</v>
+        <v>0.579</v>
       </c>
       <c r="Q18" t="n">
         <v>-0.193</v>
       </c>
       <c r="R18" t="n">
-        <v>0.965</v>
+        <v>0.772</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.1877</v>
+        <v>0.0258</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.5063</v>
+        <v>-0.1378</v>
       </c>
       <c r="U18" t="n">
-        <v>0.3186</v>
+        <v>0.1636</v>
       </c>
       <c r="V18" t="n">
-        <v>0.2859</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>0.2859</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
         <v>0</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.5898</v>
+        <v>-1.6839</v>
       </c>
       <c r="E19" t="n">
-        <v>-4.0503</v>
+        <v>-3.85</v>
       </c>
       <c r="F19" t="n">
-        <v>2.4605</v>
+        <v>2.1661</v>
       </c>
       <c r="G19" t="n">
         <v>-1.8241</v>
@@ -1936,13 +1936,13 @@
         <v>2.3161</v>
       </c>
       <c r="S19" t="n">
-        <v>0.5625</v>
+        <v>0.4683</v>
       </c>
       <c r="T19" t="n">
-        <v>-1.0417</v>
+        <v>-0.8414</v>
       </c>
       <c r="U19" t="n">
-        <v>1.6042</v>
+        <v>1.3097</v>
       </c>
       <c r="V19" t="n">
         <v>-0.3281</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.6453</v>
+        <v>-2.0504</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.9123</v>
+        <v>-0.6119</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.733</v>
+        <v>-1.4385</v>
       </c>
       <c r="G20" t="n">
         <v>-0.7578</v>
@@ -2014,13 +2014,13 @@
         <v>0.965</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.4435</v>
+        <v>0.1514</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.2247</v>
+        <v>0.0757</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.2188</v>
+        <v>0.0757</v>
       </c>
       <c r="V20" t="n">
         <v>-0.2859</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.297</v>
+        <v>-4.2875</v>
       </c>
       <c r="E21" t="n">
         <v>-5.2003</v>
       </c>
       <c r="F21" t="n">
-        <v>1.9032</v>
+        <v>0.9127999999999999</v>
       </c>
       <c r="G21" t="n">
         <v>-6.9316</v>
@@ -2092,13 +2092,13 @@
         <v>2.5091</v>
       </c>
       <c r="S21" t="n">
-        <v>2.6538</v>
+        <v>1.6634</v>
       </c>
       <c r="T21" t="n">
         <v>-0.1229</v>
       </c>
       <c r="U21" t="n">
-        <v>2.7767</v>
+        <v>1.7863</v>
       </c>
       <c r="V21" t="n">
         <v>-0.3704</v>
@@ -2125,22 +2125,22 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>6.589699999999999</v>
+        <v>6.590000000000002</v>
       </c>
       <c r="E22" t="n">
-        <v>0.752699999999999</v>
+        <v>0.7528999999999977</v>
       </c>
       <c r="F22" t="n">
-        <v>5.8369</v>
+        <v>5.837000000000001</v>
       </c>
       <c r="G22" t="n">
-        <v>-6.442900000000002</v>
+        <v>-6.4429</v>
       </c>
       <c r="H22" t="n">
         <v>-9.113199999999999</v>
       </c>
       <c r="I22" t="n">
-        <v>2.670300000000001</v>
+        <v>2.6703</v>
       </c>
       <c r="J22" t="n">
         <v>10.1698</v>
@@ -2155,7 +2155,7 @@
         <v>-16.6126</v>
       </c>
       <c r="N22" t="n">
-        <v>-4.242299999999999</v>
+        <v>-4.2423</v>
       </c>
       <c r="O22" t="n">
         <v>-12.3705</v>
@@ -2170,13 +2170,13 @@
         <v>16.4055</v>
       </c>
       <c r="S22" t="n">
-        <v>5.638199999999999</v>
+        <v>5.6382</v>
       </c>
       <c r="T22" t="n">
-        <v>-1.1368</v>
+        <v>-1.1366</v>
       </c>
       <c r="U22" t="n">
-        <v>6.774900000000001</v>
+        <v>6.7748</v>
       </c>
       <c r="V22" t="n">
         <v>4.4991</v>
